--- a/data/trans_dic/Hacinamiento_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/Hacinamiento_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación</t>
+          <t>Hogares con dos o más personas por habitación (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,62; 7,7</t>
+          <t>4,62; 7,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,01; 7,01</t>
+          <t>4,1; 6,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,53; 6,75</t>
+          <t>3,46; 6,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,33</t>
+          <t>1,55; 4,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,55; 7,17</t>
+          <t>4,57; 7,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,14; 6,61</t>
+          <t>4,15; 6,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,91; 6,86</t>
+          <t>3,94; 6,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,56; 3,72</t>
+          <t>1,55; 3,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,95; 7,0</t>
+          <t>4,93; 7,03</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,44; 6,35</t>
+          <t>4,39; 6,33</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,19; 6,22</t>
+          <t>4,16; 6,28</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,34</t>
+          <t>1,8; 3,37</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,49; 5,56</t>
+          <t>3,54; 5,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,44; 6,59</t>
+          <t>4,38; 6,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,49; 5,31</t>
+          <t>3,39; 5,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,21</t>
+          <t>1,4; 3,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,26; 7,65</t>
+          <t>5,12; 7,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,99; 8,49</t>
+          <t>6,01; 8,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 4,99</t>
+          <t>3,15; 4,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 3,73</t>
+          <t>1,95; 3,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,65; 6,28</t>
+          <t>4,64; 6,3</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,43; 7,04</t>
+          <t>5,51; 7,03</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,62; 4,89</t>
+          <t>3,56; 4,92</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,2</t>
+          <t>1,92; 3,13</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 5,72</t>
+          <t>2,33; 5,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,4</t>
+          <t>0,37; 2,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 5,28</t>
+          <t>2,17; 5,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,5</t>
+          <t>1,02; 3,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,4; 7,34</t>
+          <t>3,22; 7,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,41; 8,04</t>
+          <t>3,39; 8,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,37; 7,42</t>
+          <t>3,42; 7,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,25</t>
+          <t>0,96; 3,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,11; 5,87</t>
+          <t>3,06; 5,67</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 4,66</t>
+          <t>2,17; 4,57</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,24; 5,86</t>
+          <t>3,22; 5,77</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,81</t>
+          <t>1,2; 2,76</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 5,6</t>
+          <t>4,1; 5,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 5,56</t>
+          <t>4,02; 5,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,67; 5,08</t>
+          <t>3,71; 5,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 2,94</t>
+          <t>1,57; 2,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,17; 6,9</t>
+          <t>5,14; 6,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,44; 7,12</t>
+          <t>5,39; 7,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,88; 5,31</t>
+          <t>3,9; 5,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 3,14</t>
+          <t>1,91; 3,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,86; 6,03</t>
+          <t>4,87; 6,02</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,94; 6,11</t>
+          <t>4,94; 6,06</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,94; 4,97</t>
+          <t>3,95; 4,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 2,85</t>
+          <t>1,97; 2,87</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación</t>
+          <t>Hogares con dos o más personas por habitación (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>47476; 79134</t>
+          <t>47449; 80491</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>38877; 67987</t>
+          <t>39781; 67380</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26448; 50532</t>
+          <t>25916; 47740</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8035; 22141</t>
+          <t>7941; 22346</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>59740; 94056</t>
+          <t>59989; 97079</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>55188; 88112</t>
+          <t>55290; 86813</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38711; 67828</t>
+          <t>38965; 66677</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11638; 27707</t>
+          <t>11497; 27465</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>115929; 163754</t>
+          <t>115265; 164519</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>102280; 146236</t>
+          <t>101159; 145652</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>72909; 108109</t>
+          <t>72288; 109179</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23117; 41888</t>
+          <t>22654; 42277</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>58837; 93770</t>
+          <t>59711; 93651</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>86791; 128879</t>
+          <t>85617; 127629</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72116; 109717</t>
+          <t>70154; 109837</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31465; 73095</t>
+          <t>31861; 71967</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>83295; 121106</t>
+          <t>80952; 122142</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>104889; 148541</t>
+          <t>105096; 148030</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>63859; 98664</t>
+          <t>62278; 98628</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>42664; 82941</t>
+          <t>43270; 84628</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>152199; 205380</t>
+          <t>151758; 205899</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>201288; 261082</t>
+          <t>204142; 260680</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>146341; 198015</t>
+          <t>144096; 198913</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>85049; 144076</t>
+          <t>86175; 140962</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12233; 31524</t>
+          <t>12841; 32016</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1843; 11550</t>
+          <t>1776; 11270</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12054; 28608</t>
+          <t>11781; 29234</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6452; 22362</t>
+          <t>6510; 22025</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16177; 34913</t>
+          <t>15331; 35058</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15635; 36875</t>
+          <t>15531; 37403</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18426; 40515</t>
+          <t>18691; 40535</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6788; 21187</t>
+          <t>6289; 21035</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>31911; 60276</t>
+          <t>31427; 58229</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20330; 43818</t>
+          <t>20383; 42934</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35234; 63738</t>
+          <t>35002; 62775</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15533; 36309</t>
+          <t>15485; 35565</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>132020; 183004</t>
+          <t>133944; 187136</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>137511; 189449</t>
+          <t>136971; 189838</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>123278; 170536</t>
+          <t>124591; 172369</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>56641; 100759</t>
+          <t>53875; 101048</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>174184; 232663</t>
+          <t>173320; 231291</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>192769; 252109</t>
+          <t>190728; 249075</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>136262; 186503</t>
+          <t>137007; 188340</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>71419; 113594</t>
+          <t>69298; 115898</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>322844; 400050</t>
+          <t>323144; 399602</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>343387; 424303</t>
+          <t>342939; 421250</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>270605; 341321</t>
+          <t>271587; 342266</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>138562; 200697</t>
+          <t>138810; 202166</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Hacinamiento_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/Hacinamiento_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,62; 7,83</t>
+          <t>4,67; 7,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,1; 6,95</t>
+          <t>4,03; 6,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,46; 6,38</t>
+          <t>3,45; 6,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,37</t>
+          <t>2,1; 5,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,57; 7,4</t>
+          <t>4,61; 7,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,15; 6,52</t>
+          <t>4,15; 6,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,94; 6,74</t>
+          <t>4,07; 6,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,69</t>
+          <t>1,73; 3,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,93; 7,03</t>
+          <t>5,0; 6,97</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,39; 6,33</t>
+          <t>4,47; 6,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,16; 6,28</t>
+          <t>4,16; 6,32</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,37</t>
+          <t>2,15; 3,83</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,54; 5,55</t>
+          <t>3,52; 5,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,38; 6,52</t>
+          <t>4,23; 6,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 5,31</t>
+          <t>3,41; 5,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,16</t>
+          <t>1,98; 3,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,12; 7,72</t>
+          <t>5,24; 7,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,01; 8,46</t>
+          <t>5,92; 8,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 4,99</t>
+          <t>3,27; 5,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,81</t>
+          <t>3,01; 4,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,64; 6,3</t>
+          <t>4,68; 6,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,51; 7,03</t>
+          <t>5,45; 7,18</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,56; 4,92</t>
+          <t>3,55; 4,85</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 3,13</t>
+          <t>2,69; 3,86</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,81</t>
+          <t>2,3; 5,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,34</t>
+          <t>0,34; 2,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 5,39</t>
+          <t>2,11; 5,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,45</t>
+          <t>1,26; 3,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,22; 7,37</t>
+          <t>3,3; 7,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 8,16</t>
+          <t>3,5; 7,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 7,42</t>
+          <t>3,47; 7,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,23</t>
+          <t>1,57; 4,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,06; 5,67</t>
+          <t>3,07; 5,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,57</t>
+          <t>2,14; 4,51</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,22; 5,77</t>
+          <t>3,15; 5,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,76</t>
+          <t>1,67; 3,38</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,1; 5,73</t>
+          <t>4,08; 5,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,02; 5,57</t>
+          <t>4,1; 5,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,71; 5,13</t>
+          <t>3,64; 5,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,95</t>
+          <t>2,14; 3,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,14; 6,86</t>
+          <t>5,18; 6,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,39; 7,03</t>
+          <t>5,39; 7,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,9; 5,36</t>
+          <t>3,86; 5,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 3,2</t>
+          <t>2,77; 3,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,87; 6,02</t>
+          <t>4,81; 5,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,94; 6,06</t>
+          <t>4,92; 6,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 4,98</t>
+          <t>3,93; 4,9</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 2,87</t>
+          <t>2,61; 3,45</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13666</t>
+          <t>19015</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17691</t>
+          <t>21028</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31357</t>
+          <t>40043</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>47449; 80491</t>
+          <t>47944; 78598</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>39781; 67380</t>
+          <t>39110; 67611</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25916; 47740</t>
+          <t>25805; 50731</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7941; 22346</t>
+          <t>12062; 28776</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>59989; 97079</t>
+          <t>60441; 95320</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>55290; 86813</t>
+          <t>55250; 88709</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38965; 66677</t>
+          <t>40244; 68390</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11497; 27465</t>
+          <t>14031; 30029</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>115265; 164519</t>
+          <t>117080; 163089</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>101159; 145652</t>
+          <t>102853; 144742</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>72288; 109179</t>
+          <t>72369; 109911</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22654; 42277</t>
+          <t>29835; 53133</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50979</t>
+          <t>60298</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>61405</t>
+          <t>80811</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>112384</t>
+          <t>141109</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>59711; 93651</t>
+          <t>59459; 94328</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85617; 127629</t>
+          <t>82811; 126041</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>70154; 109837</t>
+          <t>70402; 110980</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31861; 71967</t>
+          <t>43738; 80656</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>80952; 122142</t>
+          <t>82873; 123607</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>105096; 148030</t>
+          <t>103630; 149170</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>62278; 98628</t>
+          <t>64592; 101050</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43270; 84628</t>
+          <t>64806; 101482</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>151758; 205899</t>
+          <t>152958; 207885</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>204142; 260680</t>
+          <t>201814; 266163</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>144096; 198913</t>
+          <t>143418; 196280</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>86175; 140962</t>
+          <t>117517; 168721</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11887</t>
+          <t>15716</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11890</t>
+          <t>18772</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23777</t>
+          <t>34488</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12841; 32016</t>
+          <t>12661; 32215</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1776; 11270</t>
+          <t>1618; 11325</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11781; 29234</t>
+          <t>11437; 29719</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6510; 22025</t>
+          <t>8835; 26410</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15331; 35058</t>
+          <t>15681; 35539</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15531; 37403</t>
+          <t>16067; 36640</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18691; 40535</t>
+          <t>18937; 41011</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6289; 21035</t>
+          <t>11362; 29829</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>31427; 58229</t>
+          <t>31560; 58863</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20383; 42934</t>
+          <t>20158; 42351</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35002; 62775</t>
+          <t>34325; 61246</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15485; 35565</t>
+          <t>23843; 48346</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>76532</t>
+          <t>95029</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>90986</t>
+          <t>120611</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>167518</t>
+          <t>215640</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>133944; 187136</t>
+          <t>133114; 185742</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>136971; 189838</t>
+          <t>139567; 191169</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>124591; 172369</t>
+          <t>122309; 170925</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53875; 101048</t>
+          <t>74600; 118339</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>173320; 231291</t>
+          <t>174603; 230064</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>190728; 249075</t>
+          <t>190686; 251924</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>137007; 188340</t>
+          <t>135695; 186085</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>69298; 115898</t>
+          <t>102084; 142991</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>323144; 399602</t>
+          <t>319328; 394110</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>342939; 421250</t>
+          <t>341918; 419828</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>271587; 342266</t>
+          <t>270235; 336915</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>138810; 202166</t>
+          <t>187710; 247940</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Hacinamiento_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/Hacinamiento_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación (tasa de respuesta: 99,44%)</t>
+          <t>Población en cuya vivienda residen dos o más personas por habitación (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación (tasa de respuesta: 99,44%)</t>
+          <t>Población en cuya vivienda residen dos o más personas por habitación (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
